--- a/deliverables/exports/track-a/07-customer-journey.xlsx
+++ b/deliverables/exports/track-a/07-customer-journey.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -660,75 +660,110 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Acceleration opportunities</t>
+          <t>Added from Block 1 research, what stage 1 actually is</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>• Partnerships compress stages 1 to 3. A trade body or export programme</t>
+          <t>Track A's stage 1 trigger is a founder saying target market deals close unpredictably and stall after the pitch. `00-BUYER-CHECKS.md` says where.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>introduction arrives with borrowed credibility attached, which is exactly the thing missing at stage 3. This is why Phase 8 treats partnerships as the priority channel rather than one of three.</t>
+          <t>A North American buyer runs intake, risk tiering, due diligence, contracting, operational setup and go-live, across four lanes that must all clear. Above roughly $25,000 annual contract value, procurement, legal review and a security questionnaire become normal. Above $100,000 the cycle runs 90 to 180 plus days.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>• Vertical concentration compresses stage 2 and stage 5. The second client in a</t>
+          <t>The four gaps most commonly missing from a foreign vendor's setup are mature security evidence, an accurate W-8BEN or W-8BEN-E, documented insurance at expected limits, and attributable proof assets. Three of those four are invisible to a sales team that has only ever sold at home, because the home market never asked.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>vertical gets a sharper diagnostic in less time, per Phase 1.</t>
+          <t>**Consequence for this funnel.** The diagnostic at stage 3 should test the client against these gates directly. It turns a diagnostic that currently rests on the founder's judgement into one that rests on a published checklist, which matters a great deal for a business Phase 2 scored at 1.8 on credibility.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>• Give the diagnostic away properly. Half a diagnostic is worse than none. It</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration opportunities</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>demonstrates exactly the caution that a buyer with no reference to check is watching for.</t>
+          <t>• Partnerships compress stages 1 to 3. A trade body or export programme</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>• Sell the second engagement during stage 6, not after stage 7. A client who</t>
+          <t>introduction arrives with borrowed credibility attached, which is exactly the thing missing at stage 3. This is why Phase 8 treats partnerships as the priority channel rather than one of three.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>has just seen a deal progress further than before is at the highest point of perceived value in the entire journey.</t>
+          <t>• Vertical concentration compresses stage 2 and stage 5. The second client in a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>vertical gets a sharper diagnostic in less time, per Phase 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>• Give the diagnostic away properly. Half a diagnostic is worse than none. It</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>demonstrates exactly the caution that a buyer with no reference to check is watching for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>• Sell the second engagement during stage 6, not after stage 7. A client who</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>has just seen a deal progress further than before is at the highest point of perceived value in the entire journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Carried forward</t>
         </is>
